--- a/product_upload/packages/47/file.xlsx
+++ b/product_upload/packages/47/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Gizlan</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-08D8B7DC7161</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1040,6 +1050,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Divinusmet</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-8593EA46A2DE</t>
         </is>
       </c>
@@ -1063,7 +1078,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1230,6 +1245,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Divinusmet</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-3F717B473D5A</t>
         </is>
       </c>
@@ -1253,7 +1273,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1420,6 +1440,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>Olcontro HCT</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-26ACE88D13B5</t>
         </is>
       </c>
@@ -1443,7 +1468,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1610,6 +1635,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Olcontro HCT</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-36AB23CAAB93</t>
         </is>
       </c>
@@ -1633,7 +1663,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1796,6 +1826,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>PREVYMIS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-6F37857AABD4</t>
         </is>
       </c>
@@ -1819,7 +1854,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1978,6 +2013,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Deriva BPO</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-135824D43DBC</t>
         </is>
       </c>
@@ -2001,7 +2041,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2168,6 +2208,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>Kromafina solution 4 mg/5 ml</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-BDA18B22E459</t>
         </is>
       </c>
@@ -2191,7 +2236,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2354,6 +2399,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>TERROSA</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-B6BC7D095242</t>
         </is>
       </c>
@@ -2377,7 +2427,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2548,6 +2598,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>Broncast Pediatric Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-B89069AC7053</t>
         </is>
       </c>
@@ -2571,7 +2626,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2738,6 +2793,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>CRYSVITA</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-21BA5342E151</t>
         </is>
       </c>
@@ -2761,7 +2821,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2936,6 +2996,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>LINZESS</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-89AADE8AB3EA</t>
         </is>
       </c>
@@ -2959,7 +3024,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3126,6 +3191,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>VIAGACIN</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-F73414D4734D</t>
         </is>
       </c>
@@ -3149,7 +3219,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3312,6 +3382,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>VIAGACIN</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-47D7D0135C6A</t>
         </is>
       </c>
@@ -3335,7 +3410,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3506,6 +3581,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>DULCOLAX 5MG ENTERIC COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-E4F2546F0761</t>
         </is>
       </c>
@@ -3529,7 +3609,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3692,6 +3772,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>LINZESS</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-545931829DDB</t>
         </is>
       </c>
@@ -3715,7 +3800,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3874,6 +3959,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>PRILIGY</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-D7E91D737912</t>
         </is>
       </c>
@@ -3897,7 +3987,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4052,6 +4142,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>LAYAL</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-AC26B1BA4B9F</t>
         </is>
       </c>
@@ -4075,7 +4170,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4250,6 +4345,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>HIDRASEC</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-7B64835D730C</t>
         </is>
       </c>
@@ -4273,7 +4373,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4444,6 +4544,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>HIDRASEC</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-E4653F8A6CE0</t>
         </is>
       </c>
@@ -4467,7 +4572,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4638,6 +4743,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>HIDRASEC</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-8537462A1A14</t>
         </is>
       </c>
@@ -4661,7 +4771,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4836,6 +4946,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>PROTOPIC 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-684FEFF3E699</t>
         </is>
       </c>
@@ -4859,7 +4974,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5034,6 +5149,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>PROTOPIC 0.03% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-887B93254752</t>
         </is>
       </c>
@@ -5057,7 +5177,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5216,6 +5336,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>D-Vital</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-6D05E3B84AB5</t>
         </is>
       </c>
@@ -5239,7 +5364,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5406,6 +5531,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Capillo</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-FDD4D40201B8</t>
         </is>
       </c>
@@ -5429,7 +5559,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5604,6 +5734,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Eradocin</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-FE7ACD992985</t>
         </is>
       </c>
@@ -5627,7 +5762,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5790,6 +5925,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>ERADOCIN</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-A50BD2991FBF</t>
         </is>
       </c>
@@ -5813,7 +5953,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5972,6 +6112,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>Bendy</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-8BEF85A3C36E</t>
         </is>
       </c>
@@ -5995,7 +6140,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6156,6 +6301,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>Ondans</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-84C08BE61F2F</t>
         </is>
       </c>
@@ -6179,7 +6329,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6340,6 +6490,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>Ondans</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-4DF3E20A9EDB</t>
         </is>
       </c>
@@ -6363,7 +6518,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6522,6 +6677,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-4ACBE64601C2</t>
         </is>
       </c>
@@ -6545,7 +6705,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6708,6 +6868,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-BAC8DEE7FD51</t>
         </is>
       </c>
@@ -6731,7 +6896,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6902,6 +7067,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>Aimovig</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-AF23BC4CFB7E</t>
         </is>
       </c>
@@ -6925,7 +7095,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7096,6 +7266,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Resepta</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-91DE69DE09CD</t>
         </is>
       </c>
@@ -7119,7 +7294,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7286,6 +7461,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Resepta</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-9FBE83A1AB58</t>
         </is>
       </c>
@@ -7309,7 +7489,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7482,6 +7662,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>DAVLEX</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-AC400A600974</t>
         </is>
       </c>
@@ -7505,7 +7690,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7668,6 +7853,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stablix 0.5 ml Ampules </t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-7626B232EAEA</t>
         </is>
       </c>
@@ -7691,7 +7881,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7864,6 +8054,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>LEUKAIR</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-07AAE2AD74EB</t>
         </is>
       </c>
@@ -7887,7 +8082,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8052,6 +8247,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>LEUKAIR</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-BBDEC52A032E</t>
         </is>
       </c>
@@ -8075,7 +8275,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8246,6 +8446,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Dergit</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-B24377FACC5F</t>
         </is>
       </c>
@@ -8269,7 +8474,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8440,6 +8645,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Dergit</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-61DA4B96E912</t>
         </is>
       </c>
@@ -8463,7 +8673,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8630,6 +8840,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Avoban</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-8AED3EFB6132</t>
         </is>
       </c>
@@ -8653,7 +8868,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8822,6 +9037,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>RENAPAT</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-DC5346F027FD</t>
         </is>
       </c>
@@ -8845,7 +9065,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9010,6 +9230,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>Phreno XR</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-DCDDB524508A</t>
         </is>
       </c>
@@ -9033,7 +9258,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9198,6 +9423,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Phreno XR</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-8AF33D594CC2</t>
         </is>
       </c>
@@ -9221,7 +9451,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9390,6 +9620,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>Phreno XR</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-AC9A768412CC</t>
         </is>
       </c>
@@ -9413,7 +9648,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9574,6 +9809,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>Phreno XR</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-6C89B1CFC279</t>
         </is>
       </c>
@@ -9597,7 +9837,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9762,6 +10002,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>Phreno XR</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-8BB7196F9846</t>
         </is>
       </c>
@@ -9785,7 +10030,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9950,6 +10195,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>Phreno XR</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-A0A9D6D1D952</t>
         </is>
       </c>
@@ -9973,7 +10223,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10138,6 +10388,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Phreno XR</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-A16B715F3782</t>
         </is>
       </c>
@@ -10161,7 +10416,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10326,6 +10581,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>Phreno XR</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-09BC63812C5F</t>
         </is>
       </c>
@@ -10349,7 +10609,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10516,6 +10776,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>Spravato</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-5B1C2F3360A1</t>
         </is>
       </c>
@@ -10539,7 +10804,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10702,6 +10967,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>SPRAVATO</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-9A28C780B562</t>
         </is>
       </c>
@@ -10725,7 +10995,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10892,6 +11162,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>SPRAVATO</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-D9AF519F0761</t>
         </is>
       </c>
@@ -10915,7 +11190,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11078,6 +11353,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Idacio</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-3FC0F3EC9A5B</t>
         </is>
       </c>
@@ -11101,7 +11381,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11264,6 +11544,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>Idacio</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-AF6B69C47EED</t>
         </is>
       </c>
@@ -11287,7 +11572,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11446,6 +11731,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Coufatex</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-0A2096FE1F6C</t>
         </is>
       </c>
@@ -11469,7 +11759,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11632,6 +11922,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>Coufatex</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-C824A05769C1</t>
         </is>
       </c>
@@ -11655,7 +11950,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11818,6 +12113,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Coufatex</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-8947E9BD566A</t>
         </is>
       </c>
@@ -11841,7 +12141,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12004,6 +12304,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>Coufatex</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-6BCC88E71632</t>
         </is>
       </c>
@@ -12027,7 +12332,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12198,6 +12503,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>Divido Combo</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-E27998D2A23D</t>
         </is>
       </c>
@@ -12221,7 +12531,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12388,6 +12698,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>Olneda</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-7C4060F4CEA1</t>
         </is>
       </c>
@@ -12411,7 +12726,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12578,6 +12893,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>Olneda</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-D49CFE0551B8</t>
         </is>
       </c>
@@ -12601,7 +12921,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12764,6 +13084,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>Olneda</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-CD3B17070949</t>
         </is>
       </c>
@@ -12787,7 +13112,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12958,6 +13283,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>Olneda</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-949BA156EF3F</t>
         </is>
       </c>
@@ -12981,7 +13311,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13148,6 +13478,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>Amovac Enema</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-0B9E1EE1692D</t>
         </is>
       </c>
@@ -13171,7 +13506,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13330,6 +13665,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>REYVOW</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-3290CC958FF7</t>
         </is>
       </c>
@@ -13353,7 +13693,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13516,6 +13856,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>REYVOW</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-37416A468667</t>
         </is>
       </c>
@@ -13539,7 +13884,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13710,6 +14055,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>Multifidera</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-B64E4D22502D</t>
         </is>
       </c>
@@ -13733,7 +14083,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13904,6 +14254,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>Multifidera</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-C6B8CEE47AA7</t>
         </is>
       </c>
@@ -13927,7 +14282,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14092,6 +14447,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>Lipofirate</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-0AD956191F9E</t>
         </is>
       </c>
@@ -14115,7 +14475,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14276,6 +14636,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>Plasiv</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-71C344D8ACC8</t>
         </is>
       </c>
@@ -14299,7 +14664,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14464,6 +14829,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Plasiv</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-340889FBBC11</t>
         </is>
       </c>
@@ -14487,7 +14857,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14648,6 +15018,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Plasiv</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-E64AF772F519</t>
         </is>
       </c>
@@ -14671,7 +15046,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14836,6 +15211,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Plasiv</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-3132C7231AD9</t>
         </is>
       </c>
@@ -14859,7 +15239,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15018,6 +15398,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Decryst</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-0D81ED608487</t>
         </is>
       </c>
@@ -15041,7 +15426,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15204,6 +15589,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>Decryst</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-9554D7EB656E</t>
         </is>
       </c>
@@ -15227,7 +15617,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15390,6 +15780,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>EPITAM 1000MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-C98FAC83263E</t>
         </is>
       </c>
@@ -15413,7 +15808,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15576,6 +15971,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t xml:space="preserve">VIRGAN </t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-E8C0C8C2F72F</t>
         </is>
       </c>
@@ -15599,7 +15999,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15766,6 +16166,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Doptelet</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-FF7B21BF086E</t>
         </is>
       </c>
@@ -15789,7 +16194,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15952,6 +16357,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Doptelet</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-99B1178A9A12</t>
         </is>
       </c>
@@ -15975,7 +16385,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16138,6 +16548,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Doptelet</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-D47132EC784A</t>
         </is>
       </c>
@@ -16161,7 +16576,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16320,6 +16735,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Vapress</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-B2E7CC39D850</t>
         </is>
       </c>
@@ -16343,7 +16763,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16502,6 +16922,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Vapress</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-CECD811F95F3</t>
         </is>
       </c>
@@ -16525,7 +16950,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16686,6 +17111,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>Averaz</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-B009BC4CEBE6</t>
         </is>
       </c>
@@ -16709,7 +17139,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16878,6 +17308,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>Axyla</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-E876521D1A62</t>
         </is>
       </c>
@@ -16901,7 +17336,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17064,6 +17499,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>OROTIX 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-B4B5BCBE2DE4</t>
         </is>
       </c>
@@ -17087,7 +17527,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17254,6 +17694,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>OROTIX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-DE58C3559534</t>
         </is>
       </c>
@@ -17277,7 +17722,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17444,6 +17889,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>AROX UD 0.5% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-20D7593B8372</t>
         </is>
       </c>
@@ -17467,7 +17917,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17626,6 +18076,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>ZINOLE 5MG TABLET (28 tablets)</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-CCB674EC2BBD</t>
         </is>
       </c>
@@ -17649,7 +18104,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17812,6 +18267,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t xml:space="preserve">ZINOLE 10MG TABLET (28 tablets)	</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-DD5E997796B5</t>
         </is>
       </c>
@@ -17835,7 +18295,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17994,6 +18454,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t xml:space="preserve">ZINOLE 15MG TABLET (28tablets)	</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-43DDB49BBC29</t>
         </is>
       </c>
@@ -18017,7 +18482,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18180,6 +18645,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Laroza</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-2D172CA0B557</t>
         </is>
       </c>
@@ -18203,7 +18673,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18366,6 +18836,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Laroza</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-BD694C68E1BA</t>
         </is>
       </c>
@@ -18389,7 +18864,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18552,6 +19027,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Laroza</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-1376AB4B7534</t>
         </is>
       </c>
@@ -18575,7 +19055,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18738,6 +19218,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Laroza</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-E85E469358CA</t>
         </is>
       </c>
@@ -18761,7 +19246,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18920,6 +19405,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Celer</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-E31190E58316</t>
         </is>
       </c>
@@ -18943,7 +19433,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19114,6 +19604,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Celer</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-B9FAFA31094D</t>
         </is>
       </c>
@@ -19137,7 +19632,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19308,6 +19803,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Zylone</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-9E390578857D</t>
         </is>
       </c>
@@ -19331,7 +19831,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19493,6 +19993,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Zylone</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-1174FE333F5B</t>
         </is>
@@ -19509,7 +20014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19555,100 +20060,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19680,7 +20190,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19695,92 +20205,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-82595</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>212.21</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>441</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19812,7 +20327,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19827,92 +20342,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-24672</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>349.42</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>442</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19944,7 +20464,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19959,92 +20479,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-17980</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>470.02</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>443</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20076,7 +20601,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20091,92 +20616,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-40649</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>160.14</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>444</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20208,7 +20738,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20223,92 +20753,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-33171</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>486.95</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>445</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20340,7 +20875,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20355,92 +20890,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-37477</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>458.14</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>446</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20472,7 +21012,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20487,92 +21027,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-89256</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>113.76</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>447</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20604,7 +21149,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20619,92 +21164,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-38124</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>43.65</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>448</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20736,7 +21286,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20751,92 +21301,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-54217</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>194.22</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>449</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20868,7 +21423,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20883,92 +21438,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-46071</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>106.34</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>450</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21000,7 +21560,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21015,92 +21575,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-68133</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>80.14</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>451</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21117,7 +21682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21223,6 +21788,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21258,7 +21833,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21323,6 +21898,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-74FEA0ED16C6</t>
         </is>
@@ -21359,7 +21944,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21424,6 +22009,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-1EA6D5A4426E</t>
         </is>
@@ -21460,7 +22055,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21525,6 +22120,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-BC0709108D7A</t>
         </is>
@@ -21561,7 +22166,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21626,6 +22231,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-C4C32DA987EB</t>
         </is>
@@ -21662,7 +22277,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21727,6 +22342,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-DAD1B0CC7274</t>
         </is>
@@ -21763,7 +22388,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21828,6 +22453,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-92759BD85D33</t>
         </is>
@@ -21864,7 +22499,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21929,6 +22564,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-FB8D396C4442</t>
         </is>
@@ -21965,7 +22610,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22030,6 +22675,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-6871236CC55B</t>
         </is>
@@ -22066,7 +22721,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22131,6 +22786,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-F930A31BD8EE</t>
         </is>
@@ -22167,7 +22832,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22232,6 +22897,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-C6C32FB5860B</t>
         </is>
@@ -22268,7 +22943,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22333,6 +23008,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-0D6D0E8D7BF4</t>
         </is>
@@ -22369,7 +23054,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22434,6 +23119,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-6EBBD7220591</t>
         </is>
@@ -22470,7 +23165,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22535,6 +23230,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-BAA7AAE5BF46</t>
         </is>
@@ -22571,7 +23276,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22636,6 +23341,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-04F67D8E8928</t>
         </is>
@@ -22672,7 +23387,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22737,6 +23452,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-B352EFC09243</t>
         </is>
@@ -22773,7 +23498,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22838,6 +23563,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-6FA5D3EFCDC7</t>
         </is>
@@ -22874,7 +23609,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22939,6 +23674,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-4B92B606293E</t>
         </is>
@@ -22975,7 +23720,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23040,6 +23785,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-998278BD529E</t>
         </is>
@@ -23076,7 +23831,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23141,6 +23896,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-545D07C5A449</t>
         </is>
@@ -23177,7 +23942,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23242,6 +24007,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-38488D9B06EC</t>
         </is>

--- a/product_upload/packages/47/file.xlsx
+++ b/product_upload/packages/47/file.xlsx
@@ -1281,8 +1281,16 @@
           <t>0565872893-379-045540226853</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olcontro HCT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Olcontro HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1476,8 +1484,16 @@
           <t>2907741777-735-595967223926</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olcontro HCT</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Olcontro HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1671,8 +1687,16 @@
           <t>7644272798-266-442940939463</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREVYMIS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PREVYMIS detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1862,8 +1886,16 @@
           <t>4459596515-513-106709751923</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Deriva BPO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Deriva BPO detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2244,8 +2276,16 @@
           <t>9787476208-114-934547976700</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TERROSA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TERROSA detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2634,8 +2674,16 @@
           <t>0368772931-619-648079819038</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CRYSVITA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CRYSVITA detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -3032,8 +3080,16 @@
           <t>9755175383-206-223872728003</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIAGACIN</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>VIAGACIN detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3227,8 +3283,16 @@
           <t>1078128471-671-260422853503</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIAGACIN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VIAGACIN detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3808,8 +3872,16 @@
           <t>8118738509-924-433083807399</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRILIGY</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PRILIGY detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3995,8 +4067,16 @@
           <t>8428285118-445-554722763418</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAYAL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>LAYAL detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -5185,8 +5265,16 @@
           <t>0616425746-556-599104892669</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ D-Vital</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D-Vital detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5770,8 +5858,16 @@
           <t>1893970935-369-562554408992</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ERADOCIN</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ERADOCIN detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5961,8 +6057,16 @@
           <t>5930001722-612-790944869807</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bendy</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bendy detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6148,8 +6252,16 @@
           <t>4283599373-783-650350997676</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ondans</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ondans detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -6337,8 +6449,16 @@
           <t>0637707186-487-822277450108</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ondans</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ondans detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -6526,8 +6646,16 @@
           <t>9972700621-216-526718234345</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Turbo</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Turbo detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6713,8 +6841,16 @@
           <t>2409422892-825-551900894681</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Turbo</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Turbo detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -7698,8 +7834,16 @@
           <t>9594222457-832-073820707075</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Stablix 0.5 ml Ampules</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Stablix 0.5 ml Ampules detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -8090,8 +8234,16 @@
           <t>8125766605-369-663423950765</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEUKAIR</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>LEUKAIR detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>SAUDI PHARMACEUTICAL INDUSTRIES</t>
@@ -9073,8 +9225,16 @@
           <t>8656346723-482-100655287959</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Phreno XR</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Phreno XR detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -9266,8 +9426,16 @@
           <t>7227255655-041-535035181236</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Phreno XR</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Phreno XR detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -9459,8 +9627,16 @@
           <t>4148766449-857-792215451299</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Phreno XR</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Phreno XR detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -9656,8 +9832,16 @@
           <t>9359412899-962-877227145193</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Phreno XR</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Phreno XR detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -9845,8 +10029,16 @@
           <t>8724562092-027-749843240018</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Phreno XR</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Phreno XR detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -10038,8 +10230,16 @@
           <t>8738313170-228-860432283489</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Phreno XR</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Phreno XR detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -10231,8 +10431,16 @@
           <t>4947270144-752-966585352029</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Phreno XR</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Phreno XR detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -10424,8 +10632,16 @@
           <t>6852105694-009-595249340755</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Phreno XR</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Phreno XR detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -10617,8 +10833,16 @@
           <t>6780599977-216-885346599447</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Spravato</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Spravato detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10812,8 +11036,16 @@
           <t>5386817577-520-369802772530</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPRAVATO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SPRAVATO detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -11003,8 +11235,16 @@
           <t>1959569794-313-538437386568</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPRAVATO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SPRAVATO detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11198,8 +11438,16 @@
           <t>5686919108-158-263992588916</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Idacio</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Idacio detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11389,8 +11637,16 @@
           <t>6914849727-133-955968685872</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Idacio</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Idacio detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11580,8 +11836,16 @@
           <t>9135849692-757-422882945443</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coufatex</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Coufatex detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11767,8 +12031,16 @@
           <t>8565640220-825-474225771331</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coufatex</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Coufatex detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11958,8 +12230,16 @@
           <t>2619213701-325-027243879261</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coufatex</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Coufatex detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12149,8 +12429,16 @@
           <t>7255005639-195-143726796939</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coufatex</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Coufatex detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -13514,8 +13802,16 @@
           <t>2969904672-614-838016315710</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REYVOW</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>REYVOW detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13701,8 +13997,16 @@
           <t>1853854225-691-667010982433</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REYVOW</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>REYVOW detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -14290,8 +14594,16 @@
           <t>7739737243-038-642013213221</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lipofirate</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Lipofirate detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>AL RAZI PHARMA INDUSTRIES FACTORY LTD</t>
@@ -14483,8 +14795,16 @@
           <t>4624513336-325-827967157332</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Plasiv</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Plasiv detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>Alrai Pharmaceutical industry Co. (L.L.C)</t>
@@ -14672,8 +14992,16 @@
           <t>3337713801-060-897612084048</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Plasiv</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Plasiv detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>Alrai Pharmaceutical industry Co. (L.L.C)</t>
@@ -14865,8 +15193,16 @@
           <t>9680572488-794-412224192046</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Plasiv</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Plasiv detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>Alrai Pharmaceutical industry Co. (L.L.C)</t>
@@ -15054,8 +15390,16 @@
           <t>7081427545-457-903220086286</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Plasiv</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Plasiv detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>Alrai Pharmaceutical industry Co. (L.L.C)</t>
@@ -15247,8 +15591,16 @@
           <t>5921222866-910-952161423879</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Decryst</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Decryst detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15434,8 +15786,16 @@
           <t>3294694100-861-149242341088</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Decryst</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Decryst detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15625,8 +15985,16 @@
           <t>8949529661-363-375220994478</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPITAM 1000MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>EPITAM 1000MG F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15816,8 +16184,16 @@
           <t>4132389331-757-219980480378</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRGAN</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>VIRGAN detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16007,8 +16383,16 @@
           <t>1499420068-384-879167046555</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Doptelet</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Doptelet detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16202,8 +16586,16 @@
           <t>8074753062-623-600788093248</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Doptelet</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Doptelet detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16393,8 +16785,16 @@
           <t>6302403055-588-396568425760</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Doptelet</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Doptelet detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16584,8 +16984,16 @@
           <t>1626018754-674-736778633669</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vapress</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Vapress detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16771,8 +17179,16 @@
           <t>9998651223-671-443233715675</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vapress</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Vapress detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16958,8 +17374,16 @@
           <t>7122342132-897-260928340374</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Averaz</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Averaz detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -17344,8 +17768,16 @@
           <t>9177884235-862-041075931447</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OROTIX 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>OROTIX 60MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17535,8 +17967,16 @@
           <t>9622529913-366-244468032801</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OROTIX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>OROTIX 90MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17925,8 +18365,16 @@
           <t>6467281447-733-222495718003</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZINOLE 5MG TABLET (28 tablets)</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ZINOLE 5MG TABLET (28 tablets) detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18112,8 +18560,16 @@
           <t>0017229818-772-971591351482</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZINOLE 10MG TABLET (28 tablets)</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ZINOLE 10MG TABLET (28 tablets) detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18303,8 +18759,16 @@
           <t>1976612582-180-543621820797</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZINOLE 15MG TABLET (28tablets)</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ZINOLE 15MG TABLET (28tablets) detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18490,8 +18954,16 @@
           <t>0442481709-909-670486033619</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Laroza</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Laroza detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18681,8 +19153,16 @@
           <t>5129315193-690-260473424881</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Laroza</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Laroza detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18872,8 +19352,16 @@
           <t>5306737912-315-236042250560</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Laroza</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Laroza detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19063,8 +19551,16 @@
           <t>7217870133-770-068569514326</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Laroza</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Laroza detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19254,8 +19750,16 @@
           <t>8036517480-490-760720299096</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Celer</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Celer detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19839,8 +20343,16 @@
           <t>7972300053-083-260705297101</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zylone</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Zylone detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/47/file.xlsx
+++ b/product_upload/packages/47/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22194,7 +22194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22275,40 +22275,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22388,38 +22393,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>83.26000000000001</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-74FEA0ED16C6</t>
         </is>
@@ -22499,38 +22509,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>74.86</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-1EA6D5A4426E</t>
         </is>
@@ -22610,38 +22625,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>276.13</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-BC0709108D7A</t>
         </is>
@@ -22721,38 +22741,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>369.54</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-C4C32DA987EB</t>
         </is>
@@ -22832,38 +22857,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>138.95</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-DAD1B0CC7274</t>
         </is>
@@ -22943,38 +22973,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>178.57</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-92759BD85D33</t>
         </is>
@@ -23054,38 +23089,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>431.42</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-FB8D396C4442</t>
         </is>
@@ -23165,38 +23205,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>339.37</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-6871236CC55B</t>
         </is>
@@ -23276,38 +23321,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>135.16</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-F930A31BD8EE</t>
         </is>
@@ -23387,38 +23437,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>83.83</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-C6C32FB5860B</t>
         </is>
@@ -23498,38 +23553,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>346.96</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-0D6D0E8D7BF4</t>
         </is>
@@ -23609,38 +23669,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>194.54</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-6EBBD7220591</t>
         </is>
@@ -23720,38 +23785,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>308.14</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-BAA7AAE5BF46</t>
         </is>
@@ -23831,38 +23901,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>237.96</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-04F67D8E8928</t>
         </is>
@@ -23942,38 +24017,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>204.95</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-B352EFC09243</t>
         </is>
@@ -24053,38 +24133,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>49.83</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-6FA5D3EFCDC7</t>
         </is>
@@ -24164,38 +24249,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>432.95</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-4B92B606293E</t>
         </is>
@@ -24275,38 +24365,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>355.98</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-998278BD529E</t>
         </is>
@@ -24386,38 +24481,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>231.19</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-545D07C5A449</t>
         </is>
@@ -24497,38 +24597,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>190.41</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-38488D9B06EC</t>
         </is>
